--- a/data/sample_summary/2026/Q1/Q1客户类型样本统计表.xlsx
+++ b/data/sample_summary/2026/Q1/Q1客户类型样本统计表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhangqijin/PycharmProjects/hangbo/汇总结果/Q1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhangqijin/PycharmProjects/hangbo/data/sample_summary/2026/Q1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA90978-B44F-894C-86D4-91A6CC1CC68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F600A358-D36F-454A-A99E-F1E614067497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="23040" windowHeight="23680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="46080" windowHeight="23680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="样本统计" sheetId="1" r:id="rId1"/>
@@ -591,12 +591,9 @@
   <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="33.6640625" customWidth="1"/>
-    <col min="3" max="3" width="14.1640625" customWidth="1"/>
-    <col min="4" max="4" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="36" customHeight="1">
@@ -903,14 +900,14 @@
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>6.5789473684210523E-2</v>
+        <v>5.921052631578947E-2</v>
       </c>
       <c r="E14" s="3">
         <f>SUM(F14:G14)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="3">
         <v>8</v>
@@ -950,15 +947,15 @@
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>0.18367346938775511</v>
+        <v>0.18259935553168635</v>
       </c>
       <c r="E16" s="3">
         <f>SUM(E11:E15)</f>
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F16" s="3">
         <f>SUM(F11:F15)</f>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G16" s="3">
         <f>SUM(G11:G15)</f>
@@ -1166,14 +1163,14 @@
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>8.646616541353383E-2</v>
+        <v>9.0225563909774431E-2</v>
       </c>
       <c r="E25" s="3">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F25" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G25" s="3">
         <v>6</v>
@@ -1190,15 +1187,15 @@
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>0.17833333333333334</v>
+        <v>0.18</v>
       </c>
       <c r="E26" s="3">
         <f>SUM(E21:E25)</f>
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F26" s="3">
         <f>SUM(F21:F25)</f>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G26" s="3">
         <f>SUM(G21:G25)</f>
@@ -1215,17 +1212,17 @@
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E27" s="3">
         <f>SUM(F27:G27)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="3">
         <v>0</v>
       </c>
       <c r="G27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="28" customHeight="1">
@@ -1239,11 +1236,11 @@
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>0.19359823399558498</v>
+        <v>0.19337748344370861</v>
       </c>
       <c r="E28" s="3">
         <f>SUM(E3:E9,E11:E15,E17:E18,E20:E20,E21:E25,E27:E27)</f>
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="F28" s="3">
         <f>SUM(F3:F9,F11:F15,F17:F18,F20:F20,F21:F25,F27:F27)</f>
@@ -1251,7 +1248,7 @@
       </c>
       <c r="G28" s="3">
         <f>SUM(G3:G9,G11:G15,G17:G18,G20:G20,G21:G25,G27:G27)</f>
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
   </sheetData>
